--- a/tools/luban/MiniTemplate/Datas/#demo.item.xlsx
+++ b/tools/luban/MiniTemplate/Datas/#demo.item.xlsx
@@ -2,12 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -59,6 +61,15 @@
     <t>x4</t>
   </si>
   <si>
+    <t>desc2</t>
+  </si>
+  <si>
+    <t>x5</t>
+  </si>
+  <si>
+    <t>x6</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -83,6 +94,15 @@
     <t>vector2</t>
   </si>
   <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -122,6 +142,9 @@
     <t>Circle,2,10.5</t>
   </si>
   <si>
+    <t>abc</t>
+  </si>
+  <si>
     <t>道具2</t>
   </si>
   <si>
@@ -135,6 +158,9 @@
   </si>
   <si>
     <t>Rect,3,10,20.5</t>
+  </si>
+  <si>
+    <t>var</t>
   </si>
 </sst>
 </file>
@@ -147,14 +173,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,153 +631,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1080,15 +1102,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="26.625" customWidth="1"/>
     <col min="8" max="8" width="28.75" customWidth="1"/>
+    <col min="12" max="12" width="14.125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1119,124 +1142,541 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="1">
+        <v>46033</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E6">
         <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="L6" s="1">
+        <v>46033</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5">
+        <v>1003</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="1">
+        <v>46033</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6">
+        <v>1004</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="1">
+        <v>46033</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5">
+        <v>1005</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="1">
+        <v>46033</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6">
+        <v>1006</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="1">
+        <v>46033</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/tools/luban/MiniTemplate/Datas/#demo.item.xlsx
+++ b/tools/luban/MiniTemplate/Datas/#demo.item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -142,25 +142,31 @@
     <t>Circle,2,10.5</t>
   </si>
   <si>
+    <t>k1</t>
+  </si>
+  <si>
+    <t>道具2</t>
+  </si>
+  <si>
+    <t>描述2</t>
+  </si>
+  <si>
+    <t>3|4</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>Rect,3,10,20.5</t>
+  </si>
+  <si>
+    <t>k2</t>
+  </si>
+  <si>
+    <t>var</t>
+  </si>
+  <si>
     <t>abc</t>
-  </si>
-  <si>
-    <t>道具2</t>
-  </si>
-  <si>
-    <t>描述2</t>
-  </si>
-  <si>
-    <t>3|4</t>
-  </si>
-  <si>
-    <t>3,4</t>
-  </si>
-  <si>
-    <t>Rect,3,10,20.5</t>
-  </si>
-  <si>
-    <t>var</t>
   </si>
 </sst>
 </file>
@@ -1284,6 +1290,9 @@
       <c r="J6" t="s">
         <v>41</v>
       </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
       <c r="L6" s="1">
         <v>46033</v>
       </c>
@@ -1476,6 +1485,9 @@
       <c r="J6" t="s">
         <v>41</v>
       </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
       <c r="L6" s="1">
         <v>46033</v>
       </c>
@@ -1497,7 +1509,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1634,7 +1646,7 @@
         <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L5" s="1">
         <v>46033</v>
